--- a/output/pdf_financials_xlsx/SFI.xlsx
+++ b/output/pdf_financials_xlsx/SFI.xlsx
@@ -3986,19 +3986,19 @@
         <v>0.416275</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.8347250000000001</v>
+        <v>1.158621</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>0.73339</v>
+        <v>4.699104</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>0.080599</v>
+        <v>9.650325</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>0.088699</v>
+        <v>10.335536</v>
       </c>
       <c r="P60" s="3" t="n">
-        <v>0.176654</v>
+        <v>11.697296</v>
       </c>
     </row>
     <row r="61">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -35236,10 +35236,10 @@
         </is>
       </c>
       <c r="P294" s="5" t="n">
-        <v>0.038672</v>
+        <v>-0.038672</v>
       </c>
       <c r="Q294" s="5" t="n">
-        <v>0.038672</v>
+        <v>-0.038672</v>
       </c>
       <c r="R294" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SFI.xlsx
+++ b/output/pdf_financials_xlsx/SFI.xlsx
@@ -567,20 +567,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0.003183</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.005568</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.004879</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.002591</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.003148</v>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
@@ -1362,16 +1372,16 @@
         <v>0.08432099999999999</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.016634</v>
+        <v>0.039569</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.019398</v>
+        <v>0.056698</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.017959</v>
+        <v>0.06701799999999999</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.002532</v>
+        <v>0.056206</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>2.303345</v>
@@ -1416,13 +1426,13 @@
         <v>-0.08432099999999999</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.016634</v>
+        <v>-0.039569</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.019398</v>
+        <v>-0.056698</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.017959</v>
+        <v>-0.06701799999999999</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0.056206</v>
@@ -1470,19 +1480,19 @@
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>0.003183</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>0.005568</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>0.004879</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>0.002591</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>0.003148</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
@@ -2392,19 +2402,19 @@
         <v>-0.08432099999999999</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-0.030908</v>
+        <v>-0.034091</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.020642</v>
+        <v>-0.02621</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.062139</v>
+        <v>-0.06701799999999999</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.053615</v>
+        <v>-0.056206</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.092607</v>
+        <v>1.089459</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>-1.849089</v>
@@ -2500,19 +2510,19 @@
         <v>-0.08432099999999999</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.030908</v>
+        <v>-0.034091</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-0.020642</v>
+        <v>-0.02621</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>-0.062139</v>
+        <v>-0.06701799999999999</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-0.053615</v>
+        <v>-0.056206</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1.092607</v>
+        <v>1.089459</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>-1.849089</v>
@@ -2578,7 +2588,7 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>19.58238141811307</v>
+        <v>19.52596100646988</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>-26.83289685417204</v>
@@ -3228,25 +3238,25 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>0.002339</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0</v>
+        <v>0.003872</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0</v>
+        <v>0.001024</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>0.568252</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0</v>
+        <v>0.57255</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>0.548977</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>0.493442</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.012242</v>
@@ -3332,25 +3342,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>0.002339</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>0.003872</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0</v>
+        <v>0.001024</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.568252</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>0.57255</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>0.548977</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>0.493442</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.012242</v>
@@ -15662,7 +15672,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -16865,7 +16875,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -45299,7 +45309,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -45313,16 +45323,16 @@
         </is>
       </c>
       <c r="G406" s="5" t="n">
-        <v>-0.08432099999999999</v>
+        <v>0.08432099999999999</v>
       </c>
       <c r="H406" s="5" t="n">
-        <v>-0.039569</v>
+        <v>0.039569</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>-0.056698</v>
+        <v>0.056698</v>
       </c>
       <c r="J406" s="5" t="n">
-        <v>-0.06701799999999999</v>
+        <v>0.06701799999999999</v>
       </c>
       <c r="K406" s="5" t="n">
         <v>0.056206</v>
@@ -45477,7 +45487,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -46632,7 +46642,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -48266,7 +48276,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">

--- a/output/pdf_financials_xlsx/SFI.xlsx
+++ b/output/pdf_financials_xlsx/SFI.xlsx
@@ -5046,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>0.01378</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.003658</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>-0.003658</v>
@@ -7121,10 +7121,10 @@
         <v>0.002692</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0.000763</v>
+        <v>-5.4e-05</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>7.1e-05</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -24158,7 +24158,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -26308,7 +26312,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -27924,7 +27932,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -29032,7 +29044,11 @@
           <t>Shares issued for cash 100,000</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -29958,7 +29974,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -30605,7 +30625,11 @@
           <t>HST Receivable</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -30694,7 +30718,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
